--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:16</t>
+    <t xml:space="preserve">2026-09-24 01:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>-0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.4</v>
@@ -707,7 +707,7 @@
         <v>0.07</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>-0.15</v>
@@ -730,7 +730,7 @@
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.28</v>
@@ -744,7 +744,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>21</v>
@@ -753,10 +753,10 @@
         <v>-0.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="12">
